--- a/EKG_Kalite_Yönetim_Sistemi/04_Parça ve Proses Kontrolü/02_PPC2 - MSA, Kalibrasyon ve SPC/EKG-KLT-FRM-33_cam_hatti_spc_analiz_formlari__xbar_r_ve_p_karti.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/04_Parça ve Proses Kontrolü/02_PPC2 - MSA, Kalibrasyon ve SPC/EKG-KLT-FRM-33_cam_hatti_spc_analiz_formlari__xbar_r_ve_p_karti.xlsx
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04.05.2026</t>
+          <t xml:space="preserve">10.06.2026</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,8 @@
       </ext>
     </extLst>
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-33&amp;C&amp;"Arial,Regular"&amp;11Cam Hattı SPC Analiz Formları - Xbar R ve P Kartı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 21.09.2026
+Revizyon nedeni: SPC kontrol sınırları ve geçersiz girdi denetimleri eklendi; yeterlilik yorumu kaynak kritere bağlandı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
@@ -2598,7 +2599,8 @@
       </ext>
     </extLst>
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-33&amp;C&amp;"Arial,Regular"&amp;11Cam Hattı SPC Analiz Formları - Xbar R ve P Kartı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 21.09.2026
+Revizyon nedeni: SPC kontrol sınırları ve geçersiz girdi denetimleri eklendi; yeterlilik yorumu kaynak kritere bağlandı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
